--- a/artfynd/A 34293-2023 artfynd.xlsx
+++ b/artfynd/A 34293-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34293-2023 artfynd.xlsx
+++ b/artfynd/A 34293-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>103464256</v>
       </c>
       <c r="B2" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523332.4633416774</v>
+        <v>523332</v>
       </c>
       <c r="R2" t="n">
-        <v>6619802.37170042</v>
+        <v>6619803</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,51 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111350031</v>
+        <v>111660362</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523281.2550886287</v>
+        <v>523381</v>
       </c>
       <c r="R3" t="n">
-        <v>6619910.01413854</v>
+        <v>6619759</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,42 +877,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111350516</v>
+        <v>112279685</v>
       </c>
       <c r="B4" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4404</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -967,13 +923,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523319.7728949333</v>
+        <v>523329</v>
       </c>
       <c r="R4" t="n">
-        <v>6619811.373445455</v>
+        <v>6619824</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,64 +986,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119371654</v>
+        <v>111658400</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4740</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bornsviken, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523282</v>
+        <v>523326</v>
       </c>
       <c r="R5" t="n">
-        <v>6619910</v>
+        <v>6619778</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,12 +1054,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,6 +1068,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1153,6 +1084,1282 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111350516</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>523320</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619811</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111350555</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>523346</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6619799</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112299094</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>523332</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6619814</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112279968</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>523344</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6619785</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111940426</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>523334</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6619818</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112280122</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>523356</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6619775</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112299188</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>523355</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6619797</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111660462</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>523292</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6619874</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111350031</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>523282</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6619910</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>119371654</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>523282</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6619910</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131307626</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>523281</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6619910</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>T-Lin-0070</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111660445</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>523338</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6619822</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34293-2023 artfynd.xlsx
+++ b/artfynd/A 34293-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103464256</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660362</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279685</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111658400</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350516</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350555</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299094</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279968</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940426</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280122</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299188</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1917,6 +1977,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660462</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350031</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371654</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2256,6 +2331,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131307626</t>
         </is>
       </c>
     </row>
@@ -2360,8 +2440,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660445</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>